--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4804A0D-D9CD-4B91-892C-6BDE1C542B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A404D43-5CE9-4FF6-BA4C-5FCA920C09F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26325" yWindow="945" windowWidth="24750" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>
@@ -491,7 +491,8 @@
     <col min="1" max="1" width="40.7109375" customWidth="1"/>
     <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.140625" customWidth="1"/>
-    <col min="5" max="6" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
     <col min="7" max="7" width="11.7109375" customWidth="1"/>
     <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A404D43-5CE9-4FF6-BA4C-5FCA920C09F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1EEC8E-D1C6-494F-994F-109B9EDB0FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26325" yWindow="945" windowWidth="24750" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21195" yWindow="915" windowWidth="17550" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>
@@ -138,7 +138,7 @@
     <t>26007 - OBRA HELENA Y JACOBO</t>
   </si>
   <si>
-    <t>26008 - OBRA ALBERTO Y EVA(SAN VICENTE)</t>
+    <t>26008 - OBRA ALBERTO Y EVA - C/ RIO SEGURA, 4. SAN VICENTE DEL RASPEIG</t>
   </si>
 </sst>
 </file>
@@ -177,12 +177,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -567,7 +570,7 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2">
-        <f>SUM(B4:M4)</f>
+        <f t="shared" ref="N4:N24" si="0">SUM(B4:M4)</f>
         <v>8875.66</v>
       </c>
     </row>
@@ -592,7 +595,7 @@
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2">
-        <f t="shared" ref="N5:N24" si="0">SUM(B5:M5)</f>
+        <f t="shared" si="0"/>
         <v>23917.620000000003</v>
       </c>
     </row>
@@ -1062,8 +1065,8 @@
         <v>41569.410000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="24" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B24" s="2"/>
@@ -1085,5 +1088,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1EEC8E-D1C6-494F-994F-109B9EDB0FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A95B8F4-8CAD-4165-BD1D-393155088BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21195" yWindow="915" windowWidth="17550" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -491,7 +491,7 @@
   <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.7109375" customWidth="1"/>
+    <col min="1" max="1" width="42.28515625" customWidth="1"/>
     <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.140625" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" customWidth="1"/>

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A95B8F4-8CAD-4165-BD1D-393155088BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DD4397-D682-423E-AAA8-8FB3C2F58E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>CERTIFICACIONES AÑO 2026</t>
   </si>
@@ -139,6 +139,9 @@
   </si>
   <si>
     <t>26008 - OBRA ALBERTO Y EVA - C/ RIO SEGURA, 4. SAN VICENTE DEL RASPEIG</t>
+  </si>
+  <si>
+    <t>26022 - OBRA COLEGIO MONOVAR</t>
   </si>
 </sst>
 </file>
@@ -488,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.28515625" customWidth="1"/>
@@ -570,7 +573,7 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2">
-        <f t="shared" ref="N4:N24" si="0">SUM(B4:M4)</f>
+        <f t="shared" ref="N4:N25" si="0">SUM(B4:M4)</f>
         <v>8875.66</v>
       </c>
     </row>
@@ -1086,6 +1089,15 @@
         <v>0</v>
       </c>
     </row>
+    <row r="25" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>35</v>
+      </c>
+      <c r="N25" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DD4397-D682-423E-AAA8-8FB3C2F58E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62719639-4AB8-4135-A414-CA95E1B2346C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25770" yWindow="690" windowWidth="23445" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1008,7 +1008,7 @@
         <v>9454.2800000000007</v>
       </c>
       <c r="H21" s="2">
-        <v>11518.31</v>
+        <v>5593</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
@@ -1017,7 +1017,7 @@
       <c r="M21" s="2"/>
       <c r="N21" s="2">
         <f t="shared" si="0"/>
-        <v>20972.59</v>
+        <v>15047.28</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62719639-4AB8-4135-A414-CA95E1B2346C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DB2471-CF4C-4E38-B6F7-282559A522AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25770" yWindow="690" windowWidth="23445" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>CERTIFICACIONES AÑO 2026</t>
   </si>
@@ -142,6 +142,9 @@
   </si>
   <si>
     <t>26022 - OBRA COLEGIO MONOVAR</t>
+  </si>
+  <si>
+    <t>26013 - ARREGLO PAVIMENTOS COMUNIDAD-CALLE SOROLLA, 13-EL CAMPELLO</t>
   </si>
 </sst>
 </file>
@@ -491,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.28515625" customWidth="1"/>
@@ -573,7 +576,7 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2">
-        <f t="shared" ref="N4:N25" si="0">SUM(B4:M4)</f>
+        <f t="shared" ref="N4:N26" si="0">SUM(B4:M4)</f>
         <v>8875.66</v>
       </c>
     </row>
@@ -1098,6 +1101,15 @@
         <v>0</v>
       </c>
     </row>
+    <row r="26" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N26" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5DB2471-CF4C-4E38-B6F7-282559A522AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F7F737-4DE6-4CD4-A192-F11129036247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -939,13 +939,15 @@
         <v>21606.67</v>
       </c>
       <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
+      <c r="J18" s="2">
+        <v>30413.73</v>
+      </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2">
         <f t="shared" si="0"/>
-        <v>21606.67</v>
+        <v>52020.399999999994</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -962,13 +964,15 @@
         <v>13330.32</v>
       </c>
       <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
+      <c r="J19" s="2">
+        <v>38012.910000000003</v>
+      </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
       <c r="N19" s="2">
         <f t="shared" si="0"/>
-        <v>13330.32</v>
+        <v>51343.23</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -1096,18 +1100,24 @@
       <c r="A25" t="s">
         <v>35</v>
       </c>
+      <c r="J25" s="2">
+        <v>1377.3</v>
+      </c>
       <c r="N25" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1377.3</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>36</v>
       </c>
+      <c r="J26" s="2">
+        <v>1200</v>
+      </c>
       <c r="N26" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1200</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F7F737-4DE6-4CD4-A192-F11129036247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07FEEF44-BE3C-4874-A356-0E0C8112B3AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -843,13 +843,15 @@
         <v>105666.89</v>
       </c>
       <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
+      <c r="J14" s="2">
+        <v>27426.04</v>
+      </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2">
         <f t="shared" si="0"/>
-        <v>278129.21000000002</v>
+        <v>305555.25</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -1066,13 +1068,15 @@
         <v>41569.410000000003</v>
       </c>
       <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
+      <c r="J23" s="2">
+        <v>16926.61</v>
+      </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2">
         <f t="shared" si="0"/>
-        <v>41569.410000000003</v>
+        <v>58496.020000000004</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1087,13 +1091,15 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
+      <c r="J24" s="2">
+        <v>34338.629999999997</v>
+      </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>34338.629999999997</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07FEEF44-BE3C-4874-A356-0E0C8112B3AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{044AD264-772F-49C6-AA34-2396BF702238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28770" yWindow="1080" windowWidth="23445" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>
@@ -1069,14 +1069,14 @@
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2">
-        <v>16926.61</v>
+        <v>19700.57</v>
       </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2">
         <f t="shared" si="0"/>
-        <v>58496.020000000004</v>
+        <v>61269.98</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{044AD264-772F-49C6-AA34-2396BF702238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74230E69-DDFE-4F10-B323-9424718D1740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28770" yWindow="1080" windowWidth="23445" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>
@@ -675,7 +675,7 @@
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2">
-        <v>69865.440000000002</v>
+        <v>68285.89</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -683,7 +683,7 @@
       <c r="M8" s="2"/>
       <c r="N8" s="2">
         <f t="shared" si="0"/>
-        <v>173193.43</v>
+        <v>171613.88</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74230E69-DDFE-4F10-B323-9424718D1740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C323C0DF-DADF-4BF3-BCE1-7F2DA3376B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26130" yWindow="195" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>
@@ -1044,14 +1044,14 @@
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="2">
-        <v>12022.27</v>
+        <v>14027.47</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2">
         <f t="shared" si="0"/>
-        <v>14095.61</v>
+        <v>16100.81</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C323C0DF-DADF-4BF3-BCE1-7F2DA3376B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F42A3D4-B604-47D8-A6E9-8FCAF1D44C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26130" yWindow="195" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>
@@ -144,7 +144,7 @@
     <t>26022 - OBRA COLEGIO MONOVAR</t>
   </si>
   <si>
-    <t>26013 - ARREGLO PAVIMENTOS COMUNIDAD-CALLE SOROLLA, 13-EL CAMPELLO</t>
+    <t>26013 - ARREGLO PAVIMENTOS COMUNIDAD PROPIETARIOS -CALLE SOROLLA, 13. 03560. EL CAMPELLO</t>
   </si>
 </sst>
 </file>

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F42A3D4-B604-47D8-A6E9-8FCAF1D44C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30062F3A-A385-42AA-B55E-1C5AC7958FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27285" yWindow="105" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30062F3A-A385-42AA-B55E-1C5AC7958FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7477A9A2-05A3-4F48-8ED0-1FAF06D25FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27285" yWindow="105" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26580" yWindow="780" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>
@@ -942,14 +942,14 @@
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2">
-        <v>30413.73</v>
+        <v>46160.31</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2">
         <f t="shared" si="0"/>
-        <v>52020.399999999994</v>
+        <v>67766.98</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7477A9A2-05A3-4F48-8ED0-1FAF06D25FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34ACABC3-F287-43CD-B323-040FE2F4E075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26580" yWindow="780" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26925" yWindow="435" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>
@@ -1092,14 +1092,14 @@
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2">
-        <v>34338.629999999997</v>
+        <v>33313.120000000003</v>
       </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2">
         <f t="shared" si="0"/>
-        <v>34338.629999999997</v>
+        <v>33313.120000000003</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34ACABC3-F287-43CD-B323-040FE2F4E075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0128BFB6-A36A-4B8B-A94B-666AD9FBA166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-26925" yWindow="435" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1092,14 +1092,14 @@
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2">
-        <v>33313.120000000003</v>
+        <v>32986.99</v>
       </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2">
         <f t="shared" si="0"/>
-        <v>33313.120000000003</v>
+        <v>32986.99</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0128BFB6-A36A-4B8B-A94B-666AD9FBA166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F392B1E6-EB13-4572-BA9A-386D059F31B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26925" yWindow="435" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26205" yWindow="645" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>
@@ -1092,14 +1092,14 @@
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2">
-        <v>32986.99</v>
+        <v>34049.67</v>
       </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2">
         <f t="shared" si="0"/>
-        <v>32986.99</v>
+        <v>34049.67</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F392B1E6-EB13-4572-BA9A-386D059F31B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{144366EA-37BF-4FD6-B45A-215991A577FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26205" yWindow="645" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25920" yWindow="60" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{144366EA-37BF-4FD6-B45A-215991A577FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D962B6-FC87-4148-97A4-F1CFE314CD46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25920" yWindow="60" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2130" yWindow="630" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>
@@ -497,7 +497,7 @@
   <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.28515625" customWidth="1"/>
+    <col min="1" max="1" width="51.140625" customWidth="1"/>
     <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.140625" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" customWidth="1"/>

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D962B6-FC87-4148-97A4-F1CFE314CD46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7FBA305-0EA2-4EAD-BF94-9EF40C95298F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2130" yWindow="630" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28035" yWindow="705" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>
@@ -938,18 +938,18 @@
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2">
-        <v>21606.67</v>
+        <v>7939.28</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2">
-        <v>46160.31</v>
+        <v>55435.16</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2">
         <f t="shared" si="0"/>
-        <v>67766.98</v>
+        <v>63374.44</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7FBA305-0EA2-4EAD-BF94-9EF40C95298F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8312EDB0-9E4D-406E-B29A-372DE8105C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28035" yWindow="705" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26040" yWindow="1050" windowWidth="24480" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>
@@ -1013,20 +1013,18 @@
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
-      <c r="G21" s="2">
-        <v>9454.2800000000007</v>
-      </c>
-      <c r="H21" s="2">
-        <v>5593</v>
-      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
+      <c r="J21" s="2">
+        <v>15019.02</v>
+      </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2">
         <f t="shared" si="0"/>
-        <v>15047.28</v>
+        <v>15019.02</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -1039,12 +1037,10 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-      <c r="H22" s="2">
-        <v>2073.34</v>
-      </c>
+      <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2">
-        <v>14027.47</v>
+        <v>16100.81</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8312EDB0-9E4D-406E-B29A-372DE8105C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC28AE4-EAD4-49D1-BCD7-F66E1CCC93CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26040" yWindow="1050" windowWidth="24480" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26925" yWindow="675" windowWidth="25980" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>
@@ -678,12 +678,14 @@
         <v>68285.89</v>
       </c>
       <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
+      <c r="K8" s="2">
+        <v>271.32</v>
+      </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2">
         <f t="shared" si="0"/>
-        <v>171613.88</v>
+        <v>171885.2</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC28AE4-EAD4-49D1-BCD7-F66E1CCC93CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA32F647-018E-48F6-AD43-67B817F3676A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26925" yWindow="675" windowWidth="25980" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27090" yWindow="1020" windowWidth="25980" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>
@@ -506,6 +506,7 @@
     <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.85546875" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.42578125" customWidth="1"/>
     <col min="13" max="13" width="11.28515625" customWidth="1"/>
     <col min="14" max="14" width="15.85546875" customWidth="1"/>
@@ -848,12 +849,14 @@
       <c r="J14" s="2">
         <v>27426.04</v>
       </c>
-      <c r="K14" s="2"/>
+      <c r="K14" s="2">
+        <v>59376.33</v>
+      </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2">
         <f t="shared" si="0"/>
-        <v>305555.25</v>
+        <v>364931.58</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -940,18 +943,22 @@
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2">
-        <v>7939.28</v>
-      </c>
-      <c r="I18" s="2"/>
+        <v>10790.99</v>
+      </c>
+      <c r="I18" s="2">
+        <v>974.27</v>
+      </c>
       <c r="J18" s="2">
-        <v>55435.16</v>
-      </c>
-      <c r="K18" s="2"/>
+        <v>59827.7</v>
+      </c>
+      <c r="K18" s="2">
+        <v>11074.56</v>
+      </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2">
         <f t="shared" si="0"/>
-        <v>63374.44</v>
+        <v>82667.51999999999</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -1021,12 +1028,14 @@
       <c r="J21" s="2">
         <v>15019.02</v>
       </c>
-      <c r="K21" s="2"/>
+      <c r="K21" s="2">
+        <v>9594.02</v>
+      </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2">
         <f t="shared" si="0"/>
-        <v>15019.02</v>
+        <v>24613.040000000001</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -1044,12 +1053,14 @@
       <c r="J22" s="2">
         <v>16100.81</v>
       </c>
-      <c r="K22" s="2"/>
+      <c r="K22" s="2">
+        <v>755.95</v>
+      </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2">
         <f t="shared" si="0"/>
-        <v>16100.81</v>
+        <v>16856.759999999998</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -1069,12 +1080,14 @@
       <c r="J23" s="2">
         <v>19700.57</v>
       </c>
-      <c r="K23" s="2"/>
+      <c r="K23" s="2">
+        <v>31236.84</v>
+      </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2">
         <f t="shared" si="0"/>
-        <v>61269.98</v>
+        <v>92506.82</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1092,12 +1105,14 @@
       <c r="J24" s="2">
         <v>34049.67</v>
       </c>
-      <c r="K24" s="2"/>
+      <c r="K24" s="2">
+        <v>15243.88</v>
+      </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2">
         <f t="shared" si="0"/>
-        <v>34049.67</v>
+        <v>49293.549999999996</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA32F647-018E-48F6-AD43-67B817F3676A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0A1ABC-C2CE-4786-9FC3-CB52D6E6C680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27090" yWindow="1020" windowWidth="25980" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26085" yWindow="840" windowWidth="25980" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0A1ABC-C2CE-4786-9FC3-CB52D6E6C680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651BF501-6AB3-4E77-9458-F2C6CA3EB1CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26085" yWindow="840" windowWidth="25980" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certificaciones" sheetId="1" r:id="rId1"/>
@@ -1029,13 +1029,13 @@
         <v>15019.02</v>
       </c>
       <c r="K21" s="2">
-        <v>9594.02</v>
+        <v>9352.02</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2">
         <f t="shared" si="0"/>
-        <v>24613.040000000001</v>
+        <v>24371.040000000001</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651BF501-6AB3-4E77-9458-F2C6CA3EB1CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2474C3A8-CDB0-46DF-9AA1-596583E216EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1029,13 +1029,13 @@
         <v>15019.02</v>
       </c>
       <c r="K21" s="2">
-        <v>9352.02</v>
+        <v>10116.1</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2">
         <f t="shared" si="0"/>
-        <v>24371.040000000001</v>
+        <v>25135.120000000003</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">

--- a/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
+++ b/dashboard/CERTIFICACIONES POR MESES 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2474C3A8-CDB0-46DF-9AA1-596583E216EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{916736EC-4AAB-40CB-9E59-33E5B7C24B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -978,12 +978,14 @@
       <c r="J19" s="2">
         <v>38012.910000000003</v>
       </c>
-      <c r="K19" s="2"/>
+      <c r="K19" s="2">
+        <v>958.02</v>
+      </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
       <c r="N19" s="2">
         <f t="shared" si="0"/>
-        <v>51343.23</v>
+        <v>52301.25</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
